--- a/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/Lembar_Coding_Codebook_1_0_2 (Aji).xlsx
+++ b/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/Lembar_Coding_Codebook_1_0_2 (Aji).xlsx
@@ -2154,11 +2154,12 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="11" width="10.199999999999999"/>
     <col customWidth="1" min="2" max="2" style="12" width="11.24"/>
-    <col customWidth="1" min="3" max="4" style="11" width="17.879999999999999"/>
+    <col customWidth="1" min="3" max="3" style="11" width="13.7109375"/>
+    <col customWidth="1" min="4" max="4" style="11" width="17.879999999999999"/>
     <col customWidth="1" min="5" max="5" style="12" width="66.400000000000006"/>
     <col customWidth="1" min="6" max="12" style="12" width="11.75"/>
     <col customWidth="1" min="13" max="14" style="11" width="25.539999999999999"/>
@@ -2168,7 +2169,7 @@
     <col customWidth="1" hidden="1" min="18" max="19" style="11" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" ht="36.899999999999999">
+    <row r="1" s="13" customFormat="1" ht="38.25">
       <c r="A1" s="14" t="s">
         <v>26</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v xml:space="preserve">5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="13" ht="84.049999999999997">
+    <row r="13" ht="63.75">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -3128,7 +3129,7 @@
         <v xml:space="preserve">5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="21" ht="72.25">
+    <row r="21" ht="76.5">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -3324,7 +3325,7 @@
         <v xml:space="preserve">5. Pentingnya Perlindungan Data Pribadi</v>
       </c>
     </row>
-    <row r="25" ht="72.25">
+    <row r="25" ht="76.5">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -3802,7 +3803,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="36.899999999999999">
+    <row r="35" ht="38.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -4139,7 +4140,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="107.59999999999999">
+    <row r="42" ht="114.75">
       <c r="A42" s="16">
         <v>42</v>
       </c>
@@ -4241,7 +4242,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="107.59999999999999">
+    <row r="44" ht="114.75">
       <c r="A44" s="16">
         <v>44</v>
       </c>
@@ -4625,7 +4626,7 @@
         <v xml:space="preserve">Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="52" ht="95.799999999999997">
+    <row r="52" ht="114.75">
       <c r="A52" s="16">
         <v>52</v>
       </c>
@@ -4727,7 +4728,7 @@
         <v xml:space="preserve">Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="54" ht="95.799999999999997">
+    <row r="54" ht="114.75">
       <c r="A54" s="16">
         <v>54</v>
       </c>
@@ -4829,7 +4830,7 @@
         <v xml:space="preserve">Bagian Kedua Kewajiban Pengendali Data Pribadi</v>
       </c>
     </row>
-    <row r="56" ht="95.799999999999997">
+    <row r="56" ht="114.75">
       <c r="A56" s="16">
         <v>56</v>
       </c>
@@ -6377,7 +6378,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7" disablePrompts="0">
-        <x14:dataValidation xr:uid="{1D8A62DC-6773-457B-8C67-28F93F5F6062}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{5B5C2E14-1CC3-417F-973C-ACC86749D4AE}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$5:$D$13</xm:f>
           </x14:formula1>
@@ -6386,7 +6387,7 @@
           </x14:formula2>
           <xm:sqref>F2:F86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{1E203788-21B8-472C-B7F9-CDAFFC030B4A}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{4D1E7119-118E-43AA-93E6-F5630A439835}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$16:$D$18</xm:f>
           </x14:formula1>
@@ -6395,7 +6396,7 @@
           </x14:formula2>
           <xm:sqref>G2:G86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{198310D5-38CF-4C00-AFFB-206DA14F3AA2}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{4AFD828F-BB7E-4C30-AF19-17663C37F442}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$21:$D$38</xm:f>
           </x14:formula1>
@@ -6404,7 +6405,7 @@
           </x14:formula2>
           <xm:sqref>H2:H86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{4AD8303B-8F16-4315-A5B6-7D3DAFBC9C0F}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{61143E14-FC08-4205-8F93-45B15CACFA30}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$41:$D$49</xm:f>
           </x14:formula1>
@@ -6413,7 +6414,7 @@
           </x14:formula2>
           <xm:sqref>I2:I86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{76EA071F-1925-4FC8-BE4B-1E95FB1A9806}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{5FD6A75A-6814-4EBF-AB05-FAB46805F700}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$52:$D$59</xm:f>
           </x14:formula1>
@@ -6422,7 +6423,7 @@
           </x14:formula2>
           <xm:sqref>J2:J86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{1418FA64-F96D-40D6-9664-68F6D10A450B}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{692FE73A-F986-4A7E-B36A-9F95D0DCCDC5}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$62:$D$66</xm:f>
           </x14:formula1>
@@ -6431,7 +6432,7 @@
           </x14:formula2>
           <xm:sqref>K2:K86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{782D2DAC-3880-4E21-90C1-369EFEE55B9A}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{1EE1251E-1AE1-44CD-A723-7512D4D1BECE}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$21:$D$37</xm:f>
           </x14:formula1>
